--- a/pacjenci/RYSZARD PASZKO.xlsx
+++ b/pacjenci/RYSZARD PASZKO.xlsx
@@ -413,235 +413,176 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J5"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
+          <t>Nr badania</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
           <t>Data badania</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Nr badania</t>
-        </is>
-      </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Etap leczenia</t>
+          <t>Problem kliniczny</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>Linia leczenia</t>
+          <t>Zakres badania</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Rozpoznanie</t>
+          <t>Opis badania</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Opis</t>
+          <t>Wnioski</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
           <t>SUVmax</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>Ocena odpowiedzi</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>Deauville</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>Wnioski</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
         <is>
           <t>14.03.2022</t>
         </is>
       </c>
-      <c r="B2" t="n">
-        <v>1</v>
-      </c>
       <c r="C2" t="inlineStr">
         <is>
           <t>Chłoniak Hodgkina - na podstawie badania hist-pat z węzła chłonnego okolicy lewego dołu pachowego. Ocena zaawansowania klinicznego.</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono  po 58 min od podania 18F-FDG. Glikemia:110 mg%</t>
+        </is>
+      </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>HL</t>
+          <t>: Nieznacznie asymetrycznie wzmożony metabolizm FDG w topografii prawego migdałka podniebiennego SUV max 6,8 vs 4,1strona lewa- do ew. kontroli laryngologicznej. Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Uogólniony, miernie nasilony zanik podkorowo-korowy mózgu. Drobne polipowate zgrubienia błony śluzowej w obu zatokach szczękowych. Wydatna sklerotyzacja wyrostków sutkowatych obu kości skroniowych.  Klatka piersiowa i śródpiersie: Aktywne i pobudzone metabolicznie węzły chłonne pachowe lewe wielkości do 25x13 mm SUV max do 5,3 Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Niewielkie zmiany włókniste, z nawarstwieniami opłucnowymi w szczytach obu płuc - większe po stronie prawej. Niewielkie obwodowe zmiany włókniste w płatach górnych i dolnych obu płuc. Obwodowy guzek w segmencie 6 płuca lewego średnicy 4 mm. Niewielkie zmiany włókniste obustronnie nadprzeponowo   Brzuch i miednica: Rozlanie wzmożony metabolizm FDG w jelicie grubym SUV max do 6,6- w pierwszej kolejności o charakterze czynnościowym. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Stan po cholecystektomii- w loży widoczne sa klipsy naczyniowe.  Przy dolnym biegunie śledziony - śledziona dodatkowa wielkości 18x16 mm. Mierne pogrubienie nadnercza lewego. Nerki o pozaciąganych pozapalnie obrysach. Prostata powiększona z drobnymi zwapnieniami - do kontroli urologicznej. Uchyłki esicy. Dość liczne, przeważnie drobne węzły chłonne pachwinowe obustronnie - wielkości do 11mm.   Układ kostny: Niejednorodny metabolizm FDG w układzie kostnym objętym badaniem. Zmiany zwyrodnieniowo-wytwórcze kręgosłupa.  Esowata skolioza kręgosłupa: prawowypukła na pograniczu piersiowo-lędźwiowym i lewowypukła w odcinku lędźwiowym, z rotacją kręgów. Wielopoziomowo dyskopatie i ciasne dyskopatie w odcinku szyjnym, piersiowym i lędźwiowym kręgosłupa. Dokanałowe wpuklanie się osteofitów krawędzi tylnych trzonów kręgowych - wielopoziomowo. Zmiany zwyrodnieniowo-wytwórcze w małych stawach międzykręgowych i w stawach żebrowo-poprzecznych. Zmiany zwyrodnieniowo-wytwórcze w stawach krzyżowo-biodrowych, z mostami kostnymi na przednich krawędziach. Liczne wyspy kostne w kościach miednicy oraz pojedyncza, drobna w głowie prawej kości ramiennej.  Wartości referencyjne: MBPS SUVmax 1,9; Prawy płat wątroby SUVmax do 3,1.</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Aktywna choroba</t>
+          <t>Badaniem PET/CT z 18F-FDG uwidoczniono obecność aktywnej metabolicznie choroby chłoniakowej z zajęciem węzłów chłonnych pachowych lewych. Poza tym, jak w opisie powyżej.</t>
         </is>
       </c>
       <c r="G2" t="n">
         <v>6.8</v>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>Baseline</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>Nie dotyczy</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>Aktywna metabolicznie choroba przed rozpoczęciem leczenia. Badanie wyjściowe stanowiące punkt odniesienia.</t>
-        </is>
-      </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
         <is>
           <t>06.07.2022</t>
         </is>
       </c>
-      <c r="B3" t="n">
-        <v>2</v>
-      </c>
       <c r="C3" t="inlineStr">
         <is>
           <t>Chłoniak Hodgkina - na podstawie badania hist-pat z węzła chłonnego okolicy lewego dołu pachowego. Wczesna ocena odpowiedzi.</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono  po 62 min od podania 18F-FDG. Glikemia:114 mg%</t>
+        </is>
+      </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>HL</t>
+          <t>: Nieznacznie asymetrycznie wzmożony metabolizm FDG w topografii prawego migdałka podniebiennego SUV max 5,0 vs 3,2 strona lewa- do kontroli. Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Uogólniony, miernie nasilony zanik podkorowo-korowy mózgu. Drobne polipowate zgrubienia błony śluzowej w obu zatokach szczękowych. Wydatna sklerotyzacja wyrostków sutkowatych obu kości skroniowych.  Klatka piersiowa i śródpiersie: Fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Niewielkie zmiany włókniste, z nawarstwieniami opłucnowymi w szczytach obu płuc - większe po stronie prawej. Niewielkie obwodowe zmiany włókniste w płatach górnych i dolnych obu płuc. Obwodowy guzek w segmencie 6 płuca lewego średnicy 4 mm. Niewielkie zmiany włókniste obustronnie nadprzeponowo   Brzuch i miednica: Odcinkowe pobudzenie metaboliczne w jelitach- w pierwszej kolejności o charakterze czynnościowym. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Stan po cholecystektomii- w loży widoczne sa klipsy naczyniowe.  Przy dolnym biegunie śledziony - śledziona dodatkowa wielkości 18x16 mm. Mierne pogrubienie nadnercza lewego. Nerki o pozaciąganych pozapalnie obrysach. Prostata powiększona z drobnymi zwapnieniami - do kontroli urologicznej. Uchyłki esicy. Dość liczne, przeważnie drobne węzły chłonne pachwinowe obustronnie - wielkości do 11mm.   Układ kostny: Pobudzenie metaboliczne w układzie kostnym objętym badaniem- związane ze stosowanym leczeniem?. Zmiany zwyrodnieniowo-wytwórcze kręgosłupa.  Esowata skolioza kręgosłupa: prawowypukła na pograniczu piersiowo-lędźwiowym i lewowypukła w odcinku lędźwiowym, z rotacją kręgów. Wielopoziomowo dyskopatie i ciasne dyskopatie w odcinku szyjnym, piersiowym i lędźwiowym kręgosłupa. Dokanałowe wpuklanie się osteofitów krawędzi tylnych trzonów kręgowych - wielopoziomowo. Zmiany zwyrodnieniowo-wytwórcze w małych stawach międzykręgowych i w stawach żebrowo-poprzecznych. Zmiany zwyrodnieniowo-wytwórcze w stawach krzyżowo-biodrowych, z mostami kostnymi na przednich krawędziach. Liczne wyspy kostne w kościach miednicy oraz pojedyncza, drobna w głowie prawej kości ramiennej.  Wartości referencyjne: MBPS SUVmax 1,8; Prawy płat wątroby SUVmax do 2,8.</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Do oceny</t>
+          <t>Badaniem PET/CT z 18F-FDG uwidoczniono bardzo dobrą odpowiedź choroby chłoniakowej na stosowane leczenie. Poza tym, jak w opisie powyżej.</t>
         </is>
       </c>
       <c r="G3" t="n">
         <v>5</v>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>4 - utrzymujący się wychwyt patologiczny</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>Stabilizacja choroby. Klasyfikacja Lugano: Stable Disease (SD) - stabilizacja choroby. Deauville: 4 - utrzymujący się wychwyt patologiczny.</t>
-        </is>
-      </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
         <is>
           <t>08.09.2022</t>
         </is>
       </c>
-      <c r="B4" t="n">
-        <v>3</v>
-      </c>
       <c r="C4" t="inlineStr">
         <is>
           <t>Chłoniak Hodgkina ocena remisji choroby.</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono  po 57 min od podania 18F-FDG. Glikemia:119 mg%.</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>HL</t>
+          <t>: Asymetrycznie zwiększony metabolizm FDG w topografii mięśnia skroniowego po stronie prawej, SUV max 4,8. Nieznacznie asymetrycznie wzmożony metabolizm FDG w zachyłku gruszkowatym lewym, SUV max 5,5- do ew. kontroli laryngologicznej. Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Uogólniony, miernie nasilony zanik podkorowo-korowy mózgu. Przyścienne zgrubienia błony śluzowej w zachyłku bocznym lewej zatoki klinowej. Polipowate zgrubienia błony śluzowej w obu zatokach szczękowych. Wydatna sklerotyzacja wyrostków sutkowatych obu kości skroniowych.  Klatka piersiowa i śródpiersie: Aktywny metabolicznie węzeł chłonny w górnej części prawego dołu pachowego wielkości 9mm, SUV max 4,1 [IM 96], przynaczyniowo z częściowo zachowaną zatoką - odczynowy? do kontroli. Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Niewielkie zmiany włókniste, z nawarstwieniami opłucnowymi w szczytach obu płuc - większe po stronie prawej. Niewielkie obwodowe zmiany włókniste i pojedyncze drobne guzki w płatach górnych i dolnych obu płuc. Obwodowy guzek w segmencie 6 płuca lewego średnicy 4 mm. Niewielkie pasmowate zmiany włókniste obustronnie nadprzeponowo   Brzuch i miednica: Odcinkowe pobudzenie metaboliczne w jelitach- w pierwszej kolejności o charakterze czynnościowym. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Stan po cholecystektomii- w loży widoczne są klipsy naczyniowe.  Przy dolnym biegunie śledziony - śledziona dodatkowa wielkości 18x16 mm. Mierne pogrubienie nadnercza lewego. Nerki o pozaciąganych pozapalnie obrysach. Ok. 2,5mm uwapniony konkrement w UKM-ie nerki prawej. Prostata powiększona, z drobnymi zwapnieniami. Uchyłki esicy. Dość liczne, przeważnie drobne węzły chłonne pachwinowe obustronnie - wielkości do 11mm.  Układ kostny: Pobudzenie metaboliczne w układzie kostnym objętym badaniem. Zmiany zwyrodnieniowo-wytwórcze kręgosłupa.  Esowata skolioza kręgosłupa: prawowypukła na pograniczu piersiowo-lędźwiowym i lewowypukła w odcinku lędźwiowym, z rotacją kręgów. Wielopoziomowo dyskopatie i ciasne dyskopatie w odcinku szyjnym, piersiowym i lędźwiowym kręgosłupa. Dokanałowe wpuklanie się osteofitów krawędzi tylnych trzonów kręgowych - wielopoziomowo. Zmiany zwyrodnieniowo-wytwórcze w małych stawach międzykręgowych i w stawach żebrowo-poprzecznych. Zmiany zwyrodnieniowo-wytwórcze w stawach krzyżowo-biodrowych, z mostami kostnymi na przednich krawędziach. Liczne wyspy kostne w kościach miednicy oraz pojedyncza, drobna w głowie prawej kości ramiennej.  Wartości referencyjne: MBPS SUVmax 1,8; Prawy płat wątroby SUVmax do 3,5.</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Do oceny</t>
+          <t>Badaniem PET/CT z 18F-FDG uwidoczniono aktywny metabolicznie węzeł chłonny w górnej części prawego dołu pachowego z częściowo zachowaną zatoką - odczynowy? do kontroli. Poza tym nie uwidoczniono jednoznacznych cech aktywnej metabolicznie choroby chłoniakowej. Poza tym, jak w opisie powyżej.</t>
         </is>
       </c>
       <c r="G4" t="n">
         <v>5.5</v>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>4 - utrzymujący się wychwyt patologiczny</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>Stabilizacja choroby. Klasyfikacja Lugano: Stable Disease (SD) - stabilizacja choroby. Deauville: 4 - utrzymujący się wychwyt patologiczny.</t>
-        </is>
-      </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
         <is>
           <t>11.01.2024</t>
         </is>
       </c>
-      <c r="B5" t="n">
-        <v>4</v>
-      </c>
       <c r="C5" t="inlineStr">
         <is>
           <t>Nowotwór złośliwy nasady języka. Badanie po pobraniu wycinka z nasady języka po prawej i węzła chłonnego szyi po stronie prawej. Hist-pat. rak płaskonabłonkowy związany z infekcją HPV. Przerzut raka płaskonabłonkowego do węzła chłonnego.  Cel badania - poszukiwanie ogniska pierwotnego. Chłoniak Hodgkina, stan po IVB cyklu ABVD 18.08.2022r. Ocena remisji choroby. Badanie porównano z poprzednim badaniem PET/CT z dnia 08.09.2022r.</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono  po 62 min od podania 18F-FDG. Glikemia:116 mg/dl.</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>HL</t>
+          <t>: Rozlany, niejednorodny, aktywny metabolizm FDG, SUVmax do 5,0 w topografii podniebienia oraz górnej części i nasady języka (bardziej rozległy po stronie lewej) - obraz porównywalny do badania PET z 2022r, ale aktualnie aktywność w tylnej części języka nieco wyższa niż poprzednio - obraz niecharakterystyczny, do oceny miejscowej . Aktywny metabolicznie szyjny węzeł chłonny grupy 3 po stronie prawej średnicy 8mm, SUVmax 3,5  [Im fuz 65]. Nieznacznie asymetrycznie wzmożony metabolizm FDG w zachyłku gruszkowatym lewym, SUV max 5,6 - obraz porównywalny do poprzedniego badania PET. Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Uogólniony, miernie nasilony zanik podkorowo-korowy mózgu. Przyścienne zgrubienia błony śluzowej w zachyłku bocznym lewej zatoki klinowej. Drobne polipowate zgrubienia błony śluzowej w obu zatokach szczękowych. Wydatna sklerotyzacja wyrostków sutkowatych obu kości skroniowych.  Klatka piersiowa i śródpiersie: Aktywny metabolicznie obszar w segm. 8 płuca prawego, obwodowo wielkości 9mm wg PET, bez ewidentnych zmian w miąższu płuc w przeglądowym badaniu TK, SUV max 3,5 [Im fuz 128] - do weryfikacji w badaniu TK KLP z kontrastem dożylnym. Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Niewielkie zmiany włókniste, z nawarstwieniami opłucnowymi w szczytach obu płuc - większe po stronie prawej. Niewielkie obwodowe zmiany miąższowe i drobnoguzkowe w segm. 3 płuca prawego. Niewielkie obwodowe zmiany włókniste i pojedyncze drobne guzki w płatach górnych i dolnych obu płuc. Obwodowy guzek w segmencie 6 płuca lewego średnicy 4 mm. Niewielkie pasmowate zmiany włókniste obustronnie nadprzeponowo   Brzuch i miednica: Odcinkowe pobudzenie metaboliczne w jelitach - w pierwszej kolejności o charakterze czynnościowym, porównywalnie do poprzedniego badania PET. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Stan po cholecystektomii - w loży widoczne są klipsy naczyniowe.  Przy dolnym biegunie śledziony - śledziony dodatkowe wielkości 18x16 mm oraz 12mm. Mierne pogrubienie nadnercza lewego - porównywalnie do badania z 08.2022r.. Nerki o pozaciąganych pozapalnie obrysach. Ok. 2,5mm uwapniony konkrement w UKM-ie nerki prawej. Prostata powiększona, z drobnymi zwapnieniami. Uchyłki esicy i zstępnicy. Dość liczne, przeważnie drobne węzły chłonne pachwinowe obustronnie, wielkości do 11mm - porównywalnie do poprzedniego badania PET/CT.  Układ kostny: Wzmożony metabolizm FDG w topografii dystalnych części wyrostków kolczystych L2 i L3,  SUVmax 4,2  [Im fuz 193] - w pierwszej kolejności zmiany zwyrodnieniowo-przeciążeniowo-odczynowe. Niejednorodny metabolizm FDG w układzie kostnym objętym badaniem - jak w poprzednim badaniu PET z 2022r. Zmiany zwyrodnieniowo-wytwórcze kręgosłupa.  Esowata skolioza kręgosłupa: prawowypukła na pograniczu piersiowo-lędźwiowym i lewowypukła w odcinku lędźwiowym, z rotacją kręgów. Wielopoziomowo dyskopatie i ciasne dyskopatie w odcinku szyjnym, piersiowym i lędźwiowym kręgosłupa. Dokanałowe wpuklanie się osteofitów krawędzi tylnych trzonów kręgowych - wielopoziomowo. Zmiany zwyrodnieniowo-wytwórcze w małych stawach międzykręgowych i w stawach żebrowo-poprzecznych. Zmiany zwyrodnieniowo-wytwórcze w stawach krzyżowo-biodrowych, z mostami kostnymi na przednich krawędziach. Liczne wyspy kostne w kościach miednicy oraz pojedyncza, drobna w głowie prawej kości ramiennej.  Inne: Aktywny metabolicznie obszar w topografii mięśni ręki lewej, wlk. 34x22mm wg PET, SUVmax 8,9 - na granicy badania, do oceny miejscowej, ew. w USG.  Miażdżyca aorty i tętnic potomnych.   Wartości referencyjne: MBPS SUVmax 1,9; Prawy płat wątroby SUVmax do 3,8.</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Do oceny</t>
+          <t>Badaniem PET/CT z 18F-FDG uwidoczniono aktywny metabolicznie pojedynczy węzeł chłonny w górnej części szyi po stronie prawej. Aktywny metabolicznie obszar w obwodowej części płuca prawego, bez ewidentnych zmian w przeglądowym badaniu TK - do kontroli w badaniu TK KLP z kontrastem dożylnym.  Niejednorodna aktywność w obrębie podniebienia oraz górnej części i nasady języka - obraz niecharakterystyczny, do kontroli miejscowej/laryngologicznej. Wskazana kontrola miejscowa mięśni dłoniowej strony ręki lewej - opis jak powyżej. Poza tym, jak w opisie powyżej.</t>
         </is>
       </c>
       <c r="G5" t="n">
         <v>8.9</v>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>4 - utrzymujący się wychwyt patologiczny</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>Stabilizacja choroby. Klasyfikacja Lugano: Stable Disease (SD) - stabilizacja choroby. Deauville: 4 - utrzymujący się wychwyt patologiczny.</t>
-        </is>
       </c>
     </row>
   </sheetData>

--- a/pacjenci/RYSZARD PASZKO.xlsx
+++ b/pacjenci/RYSZARD PASZKO.xlsx
@@ -413,13 +413,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:L5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Nr badania</t>
+          <t>Nr PET</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -439,17 +439,42 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Opis badania</t>
+          <t>Glikemia</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
+          <t>Czas po FDG</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Głowa i szyja</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Klatka piersiowa</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Brzuch i miednica</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Układ kostny</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
           <t>Wnioski</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>SUVmax</t>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>SUVmax_global</t>
         </is>
       </c>
     </row>
@@ -469,20 +494,45 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono  po 58 min od podania 18F-FDG. Glikemia:110 mg%</t>
+          <t>od szczytu głowy do 1/3 ud.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>: Nieznacznie asymetrycznie wzmożony metabolizm FDG w topografii prawego migdałka podniebiennego SUV max 6,8 vs 4,1strona lewa- do ew. kontroli laryngologicznej. Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Uogólniony, miernie nasilony zanik podkorowo-korowy mózgu. Drobne polipowate zgrubienia błony śluzowej w obu zatokach szczękowych. Wydatna sklerotyzacja wyrostków sutkowatych obu kości skroniowych.  Klatka piersiowa i śródpiersie: Aktywne i pobudzone metabolicznie węzły chłonne pachowe lewe wielkości do 25x13 mm SUV max do 5,3 Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Niewielkie zmiany włókniste, z nawarstwieniami opłucnowymi w szczytach obu płuc - większe po stronie prawej. Niewielkie obwodowe zmiany włókniste w płatach górnych i dolnych obu płuc. Obwodowy guzek w segmencie 6 płuca lewego średnicy 4 mm. Niewielkie zmiany włókniste obustronnie nadprzeponowo   Brzuch i miednica: Rozlanie wzmożony metabolizm FDG w jelicie grubym SUV max do 6,6- w pierwszej kolejności o charakterze czynnościowym. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Stan po cholecystektomii- w loży widoczne sa klipsy naczyniowe.  Przy dolnym biegunie śledziony - śledziona dodatkowa wielkości 18x16 mm. Mierne pogrubienie nadnercza lewego. Nerki o pozaciąganych pozapalnie obrysach. Prostata powiększona z drobnymi zwapnieniami - do kontroli urologicznej. Uchyłki esicy. Dość liczne, przeważnie drobne węzły chłonne pachwinowe obustronnie - wielkości do 11mm.   Układ kostny: Niejednorodny metabolizm FDG w układzie kostnym objętym badaniem. Zmiany zwyrodnieniowo-wytwórcze kręgosłupa.  Esowata skolioza kręgosłupa: prawowypukła na pograniczu piersiowo-lędźwiowym i lewowypukła w odcinku lędźwiowym, z rotacją kręgów. Wielopoziomowo dyskopatie i ciasne dyskopatie w odcinku szyjnym, piersiowym i lędźwiowym kręgosłupa. Dokanałowe wpuklanie się osteofitów krawędzi tylnych trzonów kręgowych - wielopoziomowo. Zmiany zwyrodnieniowo-wytwórcze w małych stawach międzykręgowych i w stawach żebrowo-poprzecznych. Zmiany zwyrodnieniowo-wytwórcze w stawach krzyżowo-biodrowych, z mostami kostnymi na przednich krawędziach. Liczne wyspy kostne w kościach miednicy oraz pojedyncza, drobna w głowie prawej kości ramiennej.  Wartości referencyjne: MBPS SUVmax 1,9; Prawy płat wątroby SUVmax do 3,1.</t>
+          <t>110</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Nieznacznie asymetrycznie wzmożony metabolizm FDG w topografii prawego migdałka podniebiennego SUV max 6,8 vs 4,1strona lewa- do ew. kontroli laryngologicznej. Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Uogólniony, miernie nasilony zanik podkorowo-korowy mózgu. Drobne polipowate zgrubienia błony śluzowej w obu zatokach szczękowych. Wydatna sklerotyzacja wyrostków sutkowatych obu kości skroniowych.</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Aktywne i pobudzone metabolicznie węzły chłonne pachowe lewe wielkości do 25x13 mm SUV max do 5,3 Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Niewielkie zmiany włókniste, z nawarstwieniami opłucnowymi w szczytach obu płuc - większe po stronie prawej. Niewielkie obwodowe zmiany włókniste w płatach górnych i dolnych obu płuc. Obwodowy guzek w segmencie 6 płuca lewego średnicy 4 mm. Niewielkie zmiany włókniste obustronnie nadprzeponowo</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Rozlanie wzmożony metabolizm FDG w jelicie grubym SUV max do 6,6- w pierwszej kolejności o charakterze czynnościowym. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Stan po cholecystektomii- w loży widoczne sa klipsy naczyniowe.  Przy dolnym biegunie śledziony - śledziona dodatkowa wielkości 18x16 mm. Mierne pogrubienie nadnercza lewego. Nerki o pozaciąganych pozapalnie obrysach. Prostata powiększona z drobnymi zwapnieniami - do kontroli urologicznej. Uchyłki esicy. Dość liczne, przeważnie drobne węzły chłonne pachwinowe obustronnie - wielkości do 11mm.</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Niejednorodny metabolizm FDG w układzie kostnym objętym badaniem. Zmiany zwyrodnieniowo-wytwórcze kręgosłupa.  Esowata skolioza kręgosłupa: prawowypukła na pograniczu piersiowo-lędźwiowym i lewowypukła w odcinku lędźwiowym, z rotacją kręgów. Wielopoziomowo dyskopatie i ciasne dyskopatie w odcinku szyjnym, piersiowym i lędźwiowym kręgosłupa. Dokanałowe wpuklanie się osteofitów krawędzi tylnych trzonów kręgowych - wielopoziomowo. Zmiany zwyrodnieniowo-wytwórcze w małych stawach międzykręgowych i w stawach żebrowo-poprzecznych. Zmiany zwyrodnieniowo-wytwórcze w stawach krzyżowo-biodrowych, z mostami kostnymi na przednich krawędziach. Liczne wyspy kostne w kościach miednicy oraz pojedyncza, drobna w głowie prawej kości ramiennej.</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
           <t>Badaniem PET/CT z 18F-FDG uwidoczniono obecność aktywnej metabolicznie choroby chłoniakowej z zajęciem węzłów chłonnych pachowych lewych. Poza tym, jak w opisie powyżej.</t>
         </is>
       </c>
-      <c r="G2" t="n">
+      <c r="L2" t="n">
         <v>6.8</v>
       </c>
     </row>
@@ -502,20 +552,45 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono  po 62 min od podania 18F-FDG. Glikemia:114 mg%</t>
+          <t>od szczytu głowy do 1/3 ud.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>: Nieznacznie asymetrycznie wzmożony metabolizm FDG w topografii prawego migdałka podniebiennego SUV max 5,0 vs 3,2 strona lewa- do kontroli. Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Uogólniony, miernie nasilony zanik podkorowo-korowy mózgu. Drobne polipowate zgrubienia błony śluzowej w obu zatokach szczękowych. Wydatna sklerotyzacja wyrostków sutkowatych obu kości skroniowych.  Klatka piersiowa i śródpiersie: Fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Niewielkie zmiany włókniste, z nawarstwieniami opłucnowymi w szczytach obu płuc - większe po stronie prawej. Niewielkie obwodowe zmiany włókniste w płatach górnych i dolnych obu płuc. Obwodowy guzek w segmencie 6 płuca lewego średnicy 4 mm. Niewielkie zmiany włókniste obustronnie nadprzeponowo   Brzuch i miednica: Odcinkowe pobudzenie metaboliczne w jelitach- w pierwszej kolejności o charakterze czynnościowym. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Stan po cholecystektomii- w loży widoczne sa klipsy naczyniowe.  Przy dolnym biegunie śledziony - śledziona dodatkowa wielkości 18x16 mm. Mierne pogrubienie nadnercza lewego. Nerki o pozaciąganych pozapalnie obrysach. Prostata powiększona z drobnymi zwapnieniami - do kontroli urologicznej. Uchyłki esicy. Dość liczne, przeważnie drobne węzły chłonne pachwinowe obustronnie - wielkości do 11mm.   Układ kostny: Pobudzenie metaboliczne w układzie kostnym objętym badaniem- związane ze stosowanym leczeniem?. Zmiany zwyrodnieniowo-wytwórcze kręgosłupa.  Esowata skolioza kręgosłupa: prawowypukła na pograniczu piersiowo-lędźwiowym i lewowypukła w odcinku lędźwiowym, z rotacją kręgów. Wielopoziomowo dyskopatie i ciasne dyskopatie w odcinku szyjnym, piersiowym i lędźwiowym kręgosłupa. Dokanałowe wpuklanie się osteofitów krawędzi tylnych trzonów kręgowych - wielopoziomowo. Zmiany zwyrodnieniowo-wytwórcze w małych stawach międzykręgowych i w stawach żebrowo-poprzecznych. Zmiany zwyrodnieniowo-wytwórcze w stawach krzyżowo-biodrowych, z mostami kostnymi na przednich krawędziach. Liczne wyspy kostne w kościach miednicy oraz pojedyncza, drobna w głowie prawej kości ramiennej.  Wartości referencyjne: MBPS SUVmax 1,8; Prawy płat wątroby SUVmax do 2,8.</t>
+          <t>114</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Nieznacznie asymetrycznie wzmożony metabolizm FDG w topografii prawego migdałka podniebiennego SUV max 5,0 vs 3,2 strona lewa- do kontroli. Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Uogólniony, miernie nasilony zanik podkorowo-korowy mózgu. Drobne polipowate zgrubienia błony śluzowej w obu zatokach szczękowych. Wydatna sklerotyzacja wyrostków sutkowatych obu kości skroniowych.</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Niewielkie zmiany włókniste, z nawarstwieniami opłucnowymi w szczytach obu płuc - większe po stronie prawej. Niewielkie obwodowe zmiany włókniste w płatach górnych i dolnych obu płuc. Obwodowy guzek w segmencie 6 płuca lewego średnicy 4 mm. Niewielkie zmiany włókniste obustronnie nadprzeponowo</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Odcinkowe pobudzenie metaboliczne w jelitach- w pierwszej kolejności o charakterze czynnościowym. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Stan po cholecystektomii- w loży widoczne sa klipsy naczyniowe.  Przy dolnym biegunie śledziony - śledziona dodatkowa wielkości 18x16 mm. Mierne pogrubienie nadnercza lewego. Nerki o pozaciąganych pozapalnie obrysach. Prostata powiększona z drobnymi zwapnieniami - do kontroli urologicznej. Uchyłki esicy. Dość liczne, przeważnie drobne węzły chłonne pachwinowe obustronnie - wielkości do 11mm.</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Pobudzenie metaboliczne w układzie kostnym objętym badaniem- związane ze stosowanym leczeniem?. Zmiany zwyrodnieniowo-wytwórcze kręgosłupa.  Esowata skolioza kręgosłupa: prawowypukła na pograniczu piersiowo-lędźwiowym i lewowypukła w odcinku lędźwiowym, z rotacją kręgów. Wielopoziomowo dyskopatie i ciasne dyskopatie w odcinku szyjnym, piersiowym i lędźwiowym kręgosłupa. Dokanałowe wpuklanie się osteofitów krawędzi tylnych trzonów kręgowych - wielopoziomowo. Zmiany zwyrodnieniowo-wytwórcze w małych stawach międzykręgowych i w stawach żebrowo-poprzecznych. Zmiany zwyrodnieniowo-wytwórcze w stawach krzyżowo-biodrowych, z mostami kostnymi na przednich krawędziach. Liczne wyspy kostne w kościach miednicy oraz pojedyncza, drobna w głowie prawej kości ramiennej.</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
           <t>Badaniem PET/CT z 18F-FDG uwidoczniono bardzo dobrą odpowiedź choroby chłoniakowej na stosowane leczenie. Poza tym, jak w opisie powyżej.</t>
         </is>
       </c>
-      <c r="G3" t="n">
+      <c r="L3" t="n">
         <v>5</v>
       </c>
     </row>
@@ -535,20 +610,45 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono  po 57 min od podania 18F-FDG. Glikemia:119 mg%.</t>
+          <t>od szczytu głowy do 1/3 ud.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>: Asymetrycznie zwiększony metabolizm FDG w topografii mięśnia skroniowego po stronie prawej, SUV max 4,8. Nieznacznie asymetrycznie wzmożony metabolizm FDG w zachyłku gruszkowatym lewym, SUV max 5,5- do ew. kontroli laryngologicznej. Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Uogólniony, miernie nasilony zanik podkorowo-korowy mózgu. Przyścienne zgrubienia błony śluzowej w zachyłku bocznym lewej zatoki klinowej. Polipowate zgrubienia błony śluzowej w obu zatokach szczękowych. Wydatna sklerotyzacja wyrostków sutkowatych obu kości skroniowych.  Klatka piersiowa i śródpiersie: Aktywny metabolicznie węzeł chłonny w górnej części prawego dołu pachowego wielkości 9mm, SUV max 4,1 [IM 96], przynaczyniowo z częściowo zachowaną zatoką - odczynowy? do kontroli. Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Niewielkie zmiany włókniste, z nawarstwieniami opłucnowymi w szczytach obu płuc - większe po stronie prawej. Niewielkie obwodowe zmiany włókniste i pojedyncze drobne guzki w płatach górnych i dolnych obu płuc. Obwodowy guzek w segmencie 6 płuca lewego średnicy 4 mm. Niewielkie pasmowate zmiany włókniste obustronnie nadprzeponowo   Brzuch i miednica: Odcinkowe pobudzenie metaboliczne w jelitach- w pierwszej kolejności o charakterze czynnościowym. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Stan po cholecystektomii- w loży widoczne są klipsy naczyniowe.  Przy dolnym biegunie śledziony - śledziona dodatkowa wielkości 18x16 mm. Mierne pogrubienie nadnercza lewego. Nerki o pozaciąganych pozapalnie obrysach. Ok. 2,5mm uwapniony konkrement w UKM-ie nerki prawej. Prostata powiększona, z drobnymi zwapnieniami. Uchyłki esicy. Dość liczne, przeważnie drobne węzły chłonne pachwinowe obustronnie - wielkości do 11mm.  Układ kostny: Pobudzenie metaboliczne w układzie kostnym objętym badaniem. Zmiany zwyrodnieniowo-wytwórcze kręgosłupa.  Esowata skolioza kręgosłupa: prawowypukła na pograniczu piersiowo-lędźwiowym i lewowypukła w odcinku lędźwiowym, z rotacją kręgów. Wielopoziomowo dyskopatie i ciasne dyskopatie w odcinku szyjnym, piersiowym i lędźwiowym kręgosłupa. Dokanałowe wpuklanie się osteofitów krawędzi tylnych trzonów kręgowych - wielopoziomowo. Zmiany zwyrodnieniowo-wytwórcze w małych stawach międzykręgowych i w stawach żebrowo-poprzecznych. Zmiany zwyrodnieniowo-wytwórcze w stawach krzyżowo-biodrowych, z mostami kostnymi na przednich krawędziach. Liczne wyspy kostne w kościach miednicy oraz pojedyncza, drobna w głowie prawej kości ramiennej.  Wartości referencyjne: MBPS SUVmax 1,8; Prawy płat wątroby SUVmax do 3,5.</t>
+          <t>119</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Asymetrycznie zwiększony metabolizm FDG w topografii mięśnia skroniowego po stronie prawej, SUV max 4,8. Nieznacznie asymetrycznie wzmożony metabolizm FDG w zachyłku gruszkowatym lewym, SUV max 5,5- do ew. kontroli laryngologicznej. Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Uogólniony, miernie nasilony zanik podkorowo-korowy mózgu. Przyścienne zgrubienia błony śluzowej w zachyłku bocznym lewej zatoki klinowej. Polipowate zgrubienia błony śluzowej w obu zatokach szczękowych. Wydatna sklerotyzacja wyrostków sutkowatych obu kości skroniowych.</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Aktywny metabolicznie węzeł chłonny w górnej części prawego dołu pachowego wielkości 9mm, SUV max 4,1 [IM 96], przynaczyniowo z częściowo zachowaną zatoką - odczynowy? do kontroli. Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Niewielkie zmiany włókniste, z nawarstwieniami opłucnowymi w szczytach obu płuc - większe po stronie prawej. Niewielkie obwodowe zmiany włókniste i pojedyncze drobne guzki w płatach górnych i dolnych obu płuc. Obwodowy guzek w segmencie 6 płuca lewego średnicy 4 mm. Niewielkie pasmowate zmiany włókniste obustronnie nadprzeponowo</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Odcinkowe pobudzenie metaboliczne w jelitach- w pierwszej kolejności o charakterze czynnościowym. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Stan po cholecystektomii- w loży widoczne są klipsy naczyniowe.  Przy dolnym biegunie śledziony - śledziona dodatkowa wielkości 18x16 mm. Mierne pogrubienie nadnercza lewego. Nerki o pozaciąganych pozapalnie obrysach. Ok. 2,5mm uwapniony konkrement w UKM-ie nerki prawej. Prostata powiększona, z drobnymi zwapnieniami. Uchyłki esicy. Dość liczne, przeważnie drobne węzły chłonne pachwinowe obustronnie - wielkości do 11mm.</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Pobudzenie metaboliczne w układzie kostnym objętym badaniem. Zmiany zwyrodnieniowo-wytwórcze kręgosłupa.  Esowata skolioza kręgosłupa: prawowypukła na pograniczu piersiowo-lędźwiowym i lewowypukła w odcinku lędźwiowym, z rotacją kręgów. Wielopoziomowo dyskopatie i ciasne dyskopatie w odcinku szyjnym, piersiowym i lędźwiowym kręgosłupa. Dokanałowe wpuklanie się osteofitów krawędzi tylnych trzonów kręgowych - wielopoziomowo. Zmiany zwyrodnieniowo-wytwórcze w małych stawach międzykręgowych i w stawach żebrowo-poprzecznych. Zmiany zwyrodnieniowo-wytwórcze w stawach krzyżowo-biodrowych, z mostami kostnymi na przednich krawędziach. Liczne wyspy kostne w kościach miednicy oraz pojedyncza, drobna w głowie prawej kości ramiennej.</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
           <t>Badaniem PET/CT z 18F-FDG uwidoczniono aktywny metabolicznie węzeł chłonny w górnej części prawego dołu pachowego z częściowo zachowaną zatoką - odczynowy? do kontroli. Poza tym nie uwidoczniono jednoznacznych cech aktywnej metabolicznie choroby chłoniakowej. Poza tym, jak w opisie powyżej.</t>
         </is>
       </c>
-      <c r="G4" t="n">
+      <c r="L4" t="n">
         <v>5.5</v>
       </c>
     </row>
@@ -568,20 +668,45 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono  po 62 min od podania 18F-FDG. Glikemia:116 mg/dl.</t>
+          <t>od szczytu głowy do 1/3 ud.</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>: Rozlany, niejednorodny, aktywny metabolizm FDG, SUVmax do 5,0 w topografii podniebienia oraz górnej części i nasady języka (bardziej rozległy po stronie lewej) - obraz porównywalny do badania PET z 2022r, ale aktualnie aktywność w tylnej części języka nieco wyższa niż poprzednio - obraz niecharakterystyczny, do oceny miejscowej . Aktywny metabolicznie szyjny węzeł chłonny grupy 3 po stronie prawej średnicy 8mm, SUVmax 3,5  [Im fuz 65]. Nieznacznie asymetrycznie wzmożony metabolizm FDG w zachyłku gruszkowatym lewym, SUV max 5,6 - obraz porównywalny do poprzedniego badania PET. Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Uogólniony, miernie nasilony zanik podkorowo-korowy mózgu. Przyścienne zgrubienia błony śluzowej w zachyłku bocznym lewej zatoki klinowej. Drobne polipowate zgrubienia błony śluzowej w obu zatokach szczękowych. Wydatna sklerotyzacja wyrostków sutkowatych obu kości skroniowych.  Klatka piersiowa i śródpiersie: Aktywny metabolicznie obszar w segm. 8 płuca prawego, obwodowo wielkości 9mm wg PET, bez ewidentnych zmian w miąższu płuc w przeglądowym badaniu TK, SUV max 3,5 [Im fuz 128] - do weryfikacji w badaniu TK KLP z kontrastem dożylnym. Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Niewielkie zmiany włókniste, z nawarstwieniami opłucnowymi w szczytach obu płuc - większe po stronie prawej. Niewielkie obwodowe zmiany miąższowe i drobnoguzkowe w segm. 3 płuca prawego. Niewielkie obwodowe zmiany włókniste i pojedyncze drobne guzki w płatach górnych i dolnych obu płuc. Obwodowy guzek w segmencie 6 płuca lewego średnicy 4 mm. Niewielkie pasmowate zmiany włókniste obustronnie nadprzeponowo   Brzuch i miednica: Odcinkowe pobudzenie metaboliczne w jelitach - w pierwszej kolejności o charakterze czynnościowym, porównywalnie do poprzedniego badania PET. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Stan po cholecystektomii - w loży widoczne są klipsy naczyniowe.  Przy dolnym biegunie śledziony - śledziony dodatkowe wielkości 18x16 mm oraz 12mm. Mierne pogrubienie nadnercza lewego - porównywalnie do badania z 08.2022r.. Nerki o pozaciąganych pozapalnie obrysach. Ok. 2,5mm uwapniony konkrement w UKM-ie nerki prawej. Prostata powiększona, z drobnymi zwapnieniami. Uchyłki esicy i zstępnicy. Dość liczne, przeważnie drobne węzły chłonne pachwinowe obustronnie, wielkości do 11mm - porównywalnie do poprzedniego badania PET/CT.  Układ kostny: Wzmożony metabolizm FDG w topografii dystalnych części wyrostków kolczystych L2 i L3,  SUVmax 4,2  [Im fuz 193] - w pierwszej kolejności zmiany zwyrodnieniowo-przeciążeniowo-odczynowe. Niejednorodny metabolizm FDG w układzie kostnym objętym badaniem - jak w poprzednim badaniu PET z 2022r. Zmiany zwyrodnieniowo-wytwórcze kręgosłupa.  Esowata skolioza kręgosłupa: prawowypukła na pograniczu piersiowo-lędźwiowym i lewowypukła w odcinku lędźwiowym, z rotacją kręgów. Wielopoziomowo dyskopatie i ciasne dyskopatie w odcinku szyjnym, piersiowym i lędźwiowym kręgosłupa. Dokanałowe wpuklanie się osteofitów krawędzi tylnych trzonów kręgowych - wielopoziomowo. Zmiany zwyrodnieniowo-wytwórcze w małych stawach międzykręgowych i w stawach żebrowo-poprzecznych. Zmiany zwyrodnieniowo-wytwórcze w stawach krzyżowo-biodrowych, z mostami kostnymi na przednich krawędziach. Liczne wyspy kostne w kościach miednicy oraz pojedyncza, drobna w głowie prawej kości ramiennej.  Inne: Aktywny metabolicznie obszar w topografii mięśni ręki lewej, wlk. 34x22mm wg PET, SUVmax 8,9 - na granicy badania, do oceny miejscowej, ew. w USG.  Miażdżyca aorty i tętnic potomnych.   Wartości referencyjne: MBPS SUVmax 1,9; Prawy płat wątroby SUVmax do 3,8.</t>
+          <t>116</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Rozlany, niejednorodny, aktywny metabolizm FDG, SUVmax do 5,0 w topografii podniebienia oraz górnej części i nasady języka (bardziej rozległy po stronie lewej) - obraz porównywalny do badania PET z 2022r, ale aktualnie aktywność w tylnej części języka nieco wyższa niż poprzednio - obraz niecharakterystyczny, do oceny miejscowej . Aktywny metabolicznie szyjny węzeł chłonny grupy 3 po stronie prawej średnicy 8mm, SUVmax 3,5  [Im fuz 65]. Nieznacznie asymetrycznie wzmożony metabolizm FDG w zachyłku gruszkowatym lewym, SUV max 5,6 - obraz porównywalny do poprzedniego badania PET. Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Uogólniony, miernie nasilony zanik podkorowo-korowy mózgu. Przyścienne zgrubienia błony śluzowej w zachyłku bocznym lewej zatoki klinowej. Drobne polipowate zgrubienia błony śluzowej w obu zatokach szczękowych. Wydatna sklerotyzacja wyrostków sutkowatych obu kości skroniowych.</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Aktywny metabolicznie obszar w segm. 8 płuca prawego, obwodowo wielkości 9mm wg PET, bez ewidentnych zmian w miąższu płuc w przeglądowym badaniu TK, SUV max 3,5 [Im fuz 128] - do weryfikacji w badaniu TK KLP z kontrastem dożylnym. Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Niewielkie zmiany włókniste, z nawarstwieniami opłucnowymi w szczytach obu płuc - większe po stronie prawej. Niewielkie obwodowe zmiany miąższowe i drobnoguzkowe w segm. 3 płuca prawego. Niewielkie obwodowe zmiany włókniste i pojedyncze drobne guzki w płatach górnych i dolnych obu płuc. Obwodowy guzek w segmencie 6 płuca lewego średnicy 4 mm. Niewielkie pasmowate zmiany włókniste obustronnie nadprzeponowo</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Odcinkowe pobudzenie metaboliczne w jelitach - w pierwszej kolejności o charakterze czynnościowym, porównywalnie do poprzedniego badania PET. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Stan po cholecystektomii - w loży widoczne są klipsy naczyniowe.  Przy dolnym biegunie śledziony - śledziony dodatkowe wielkości 18x16 mm oraz 12mm. Mierne pogrubienie nadnercza lewego - porównywalnie do badania z 08.2022r.. Nerki o pozaciąganych pozapalnie obrysach. Ok. 2,5mm uwapniony konkrement w UKM-ie nerki prawej. Prostata powiększona, z drobnymi zwapnieniami. Uchyłki esicy i zstępnicy. Dość liczne, przeważnie drobne węzły chłonne pachwinowe obustronnie, wielkości do 11mm - porównywalnie do poprzedniego badania PET/CT.</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Wzmożony metabolizm FDG w topografii dystalnych części wyrostków kolczystych L2 i L3,  SUVmax 4,2  [Im fuz 193] - w pierwszej kolejności zmiany zwyrodnieniowo-przeciążeniowo-odczynowe. Niejednorodny metabolizm FDG w układzie kostnym objętym badaniem - jak w poprzednim badaniu PET z 2022r. Zmiany zwyrodnieniowo-wytwórcze kręgosłupa.  Esowata skolioza kręgosłupa: prawowypukła na pograniczu piersiowo-lędźwiowym i lewowypukła w odcinku lędźwiowym, z rotacją kręgów. Wielopoziomowo dyskopatie i ciasne dyskopatie w odcinku szyjnym, piersiowym i lędźwiowym kręgosłupa. Dokanałowe wpuklanie się osteofitów krawędzi tylnych trzonów kręgowych - wielopoziomowo. Zmiany zwyrodnieniowo-wytwórcze w małych stawach międzykręgowych i w stawach żebrowo-poprzecznych. Zmiany zwyrodnieniowo-wytwórcze w stawach krzyżowo-biodrowych, z mostami kostnymi na przednich krawędziach. Liczne wyspy kostne w kościach miednicy oraz pojedyncza, drobna w głowie prawej kości ramiennej.  Inne: Aktywny metabolicznie obszar w topografii mięśni ręki lewej, wlk. 34x22mm wg PET, SUVmax 8,9 - na granicy badania, do oceny miejscowej, ew. w USG.  Miażdżyca aorty i tętnic potomnych.</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
           <t>Badaniem PET/CT z 18F-FDG uwidoczniono aktywny metabolicznie pojedynczy węzeł chłonny w górnej części szyi po stronie prawej. Aktywny metabolicznie obszar w obwodowej części płuca prawego, bez ewidentnych zmian w przeglądowym badaniu TK - do kontroli w badaniu TK KLP z kontrastem dożylnym.  Niejednorodna aktywność w obrębie podniebienia oraz górnej części i nasady języka - obraz niecharakterystyczny, do kontroli miejscowej/laryngologicznej. Wskazana kontrola miejscowa mięśni dłoniowej strony ręki lewej - opis jak powyżej. Poza tym, jak w opisie powyżej.</t>
         </is>
       </c>
-      <c r="G5" t="n">
+      <c r="L5" t="n">
         <v>8.9</v>
       </c>
     </row>
